--- a/tools/excel-config/player.xlsx
+++ b/tools/excel-config/player.xlsx
@@ -675,7 +675,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>受击判定半径 px（建议 24~28，越小越耐玩）</t>
+          <t>受击判定半径 px（建议 45，越小越耐玩）</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>贴图名</t>
+          <t>玩家贴图名（player_001）</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
@@ -754,13 +754,13 @@
         <v>100</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>320</v>
+        <v>512</v>
       </c>
       <c r="G4" s="4" t="n">
         <v>5</v>
@@ -769,29 +769,29 @@
         <v>0.35</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>900</v>
+        <v>1440</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="M4" s="4" t="n">
         <v>8</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>120</v>
+        <v>192</v>
       </c>
       <c r="O4" s="4" t="n">
         <v>8</v>
       </c>
       <c r="P4" s="4" t="inlineStr">
         <is>
-          <t>game_player</t>
+          <t>player_001</t>
         </is>
       </c>
       <c r="Q4" s="4" t="inlineStr">
